--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_459_Malaysia_Peninsula_West.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_459_Malaysia_Peninsula_West.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Re34943ef62af4874"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Re1d4c15081274b28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R0d6dc12b9a2846f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R44b7f16a79bd450b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rab6901e1c83b4acc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R3f82328b13244a28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R63c20260fe394225"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R1e569d9eeaad4b0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R91114632fa554780"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rcc00a26fbb1e4805"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R2e6011df8f494af3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R24ad0a933c754468"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ459CommercialTable" displayName="EEZ459CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ459CommercialTable" displayName="EEZ459CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ459FunctionalTable" displayName="EEZ459FunctionalTable" ref="A1:O21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O21"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ459FunctionalTable" displayName="EEZ459FunctionalTable" ref="A1:E21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E21"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ459ValidationTable" displayName="EEZ459ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ459ValidationTable" displayName="EEZ459ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -10945,7 +10899,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bbc8129a6da4375"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d8177f3c3c64fcf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10955,20 +10909,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -10976,606 +10920,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>46330.81551019599</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.4260703039033897</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>266.7290412466921</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>46330.81551019599</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>267.77805871603766</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$154,A2,'Species'!$U$2:$U$154))</x:f>
-        <x:v>12406375.83605117</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.4260703039033897</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>266.7290412466921</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>12357774.001211949</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>48601.83483922109</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0039328955873812</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0039328955873812405</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>146951.8685939225</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.834707340364332</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>68.34509324485899</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>146951.8685939225</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>112.21751250702302</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$154,A3,'Species'!$U$2:$U$154))</x:f>
-        <x:v>16490573.1518689</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.834707340364332</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>68.34509324485899</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>10043439.161557898</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>6447133.990311002</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.6419249309527304</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.6419249309527304</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>8674.151263038999</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.503404236717906</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>318.7162718929465</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>8674.151263038999</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>356.34176484089755</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$154,A4,'Species'!$U$2:$U$154))</x:f>
-        <x:v>3090962.3695682175</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.503404236717906</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>318.7162718929465</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>2764593.152391283</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>326369.2171769347</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.1180532538375985</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.11805325383759849</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>17698.6182737621</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.3624841178182123</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>230.40087167435325</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>17698.6182737621</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>505.94603149743006</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$154,A5,'Species'!$U$2:$U$154))</x:f>
-        <x:v>8954545.67859783</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.3624841178182123</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>230.40087167435325</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>4077777.0777064245</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>4876768.600891406</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>2.1959380093515017</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>1.1959380093515017</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>1995.8212540607</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.08716811853845</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>12.22272719216135</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>1995.8212540607</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>12.257004098789084</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$154,A6,'Species'!$U$2:$U$154))</x:f>
-        <x:v>24462.78929147237</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.08716811853845</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>12.22272719216135</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>24394.378712701287</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>68.41057877108324</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0028043583145434</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.002804358314543353</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>222488.93921292908</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.624740013636457</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>421.44413427477116</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>222488.93921292908</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>780.4123422451047</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$154,A7,'Species'!$U$2:$U$154))</x:f>
-        <x:v>173633114.1747907</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.624740013636457</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>421.44413427477116</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>93766658.37230508</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>79866455.80248563</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.8517575136928948</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.8517575136928948</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>650708.1834964441</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.4408200696847815</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>275.94343722855217</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>650708.1834964441</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>481.615509457606</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$154,A8,'Species'!$U$2:$U$154))</x:f>
-        <x:v>313391153.3028733</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.4408200696847815</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>275.94343722855217</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>179558652.78675625</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>133832500.51611707</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.7453414159609255</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.7453414159609254</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>3819.250380699</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.9071946219241807</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>807.5968604097366</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>3819.250380699</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>807.7949612628532</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$154,A9,'Species'!$U$2:$U$154))</x:f>
-        <x:v>3085171.213329886</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.9071946219241807</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>807.5968604097366</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>3084414.6165712033</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>756.5967586827464</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.000245296710312</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.0002452967103118643</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>8491.5141565541</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.941313878296392</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>873.6025203318908</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>8491.5141565541</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>955.6526004342332</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$154,A10,'Species'!$U$2:$U$154))</x:f>
-        <x:v>8114937.58533503</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.941313878296392</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>873.6025203318908</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>7418208.168599592</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>696729.4167354386</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.09392152402579</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.09392152402579006</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>2680.1242957115996</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.391184187191184</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2461.411283785736</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>2680.1242957115996</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2494.432736833107</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$154,A11,'Species'!$U$2:$U$154))</x:f>
-        <x:v>6685389.7820047885</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.391184187191184</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2461.411283785736</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>6596888.18341283</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>88501.59859195817</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0134156584333938</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.01341565843339379</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80a7d38533444fbb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbcf83f0907034d7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11585,20 +11135,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -11606,1146 +11146,402 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>25949.585675891798</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.6872233790537186</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>486.65745323890246</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>25949.585675891798</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>488.40660896036485</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$154,A2,'Species'!$U$2:$U$154))</x:f>
-        <x:v>12673949.14388877</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.6872233790537186</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>486.65745323890246</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>12628559.277634205</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>45389.866254564375</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0035942236368127</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.003594223636812795</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>436.0585460468</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.46</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>288.40315031266056</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>436.0585460468</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$154,A3,'Species'!$U$2:$U$154))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>125760.65840065548</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.46</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>125760.65840065548</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>20648.997692438403</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.4174683977738365</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2614.9801574376534</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>20648.997692438403</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2619.7601562669493</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$154,A4,'Species'!$U$2:$U$154))</x:f>
-        <x:v>54095421.421498306</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.4174683977738365</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2614.9801574376534</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>53996719.236702316</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>98702.18479599059</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.00182792929258</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0018279292925800824</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>3312.3320406513994</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.0583028705960436</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1143.6756393444248</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>3312.3320406513994</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1221.593054590098</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$154,A5,'Species'!$U$2:$U$154))</x:f>
-        <x:v>4046321.8153559957</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.0583028705960436</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1143.6756393444248</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>3788233.4643130125</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>258088.35104298312</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0681289454502474</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.06812894545024745</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>16507.931854848994</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.345633192104901</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2216.3237078905645</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>16507.931854848994</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2250.9659597255995</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$154,A6,'Species'!$U$2:$U$154))</x:f>
-        <x:v>37158792.670734964</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.345633192104901</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2216.3237078905645</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>36586920.73814368</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>571871.9325912818</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0156305018584162</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.01563050185841622</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>6596.1606996324</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.8498501793550504</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>707.7016030609313</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>6596.1606996324</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>707.7347236007778</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$154,A7,'Species'!$U$2:$U$154))</x:f>
-        <x:v>4668331.969580649</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.8498501793550504</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>707.7016030609313</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>4668113.501177364</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>218.46840328536928</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0000468001481178</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.00004680014811770718</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>6329.4088942524</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.615238574654408</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>412.3239622980383</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>6329.4088942524</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>515.9902513887424</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$154,A8,'Species'!$U$2:$U$154))</x:f>
-        <x:v>3265913.2864874383</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.615238574654408</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>412.3239622980383</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>2609766.954282595</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>656146.3322048434</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.2514195112816933</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.2514195112816934</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1895.3534569216997</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.25962350766744</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1818.1240332641842</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1895.3534569216997</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1818.4500643759166</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$154,A9,'Species'!$U$2:$U$154))</x:f>
-        <x:v>3446605.615754381</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.25962350766744</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1818.1240332641842</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>3445987.6715596947</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>617.9441946861334</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0001793228106375</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.00017932281063746364</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>8616.4502758628</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>2.642970581109062</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>43.9511842117112</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>8616.4502758628</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>57.95109242206718</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$154,A10,'Species'!$U$2:$U$154))</x:f>
-        <x:v>499332.7062866714</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>2.642970581109062</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>43.9511842117112</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>378703.19332549575</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>120629.51296117564</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.318533128548231</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.3185331285482308</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>43483.55223426621</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.6174565655169917</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>414.4351336472625</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>43483.55223426621</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>461.22068156909904</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$154,A11,'Species'!$U$2:$U$154))</x:f>
-        <x:v>20055513.59853378</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.6174565655169917</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>414.4351336472625</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>18021111.781665836</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>2034401.8168679439</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1128899171990978</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.1128899171990979</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>213122.51568778083</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.606754089309827</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>404.34687341786486</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>213122.51568778083</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>782.7398664907774</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$154,A12,'Species'!$U$2:$U$154))</x:f>
-        <x:v>166819489.4756322</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.606754089309827</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>404.34687341786486</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>86175422.87330404</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>80644066.60232815</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.9358128328640969</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.935812832864097</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>405798.6725558962</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.312262008829885</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>205.2400013452241</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>405798.6725558962</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>355.9764418489692</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$154,A13,'Species'!$U$2:$U$154))</x:f>
-        <x:v>144454767.56348288</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.312262008829885</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>205.2400013452241</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>83286120.1012623</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>61168647.46222058</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.7344398729085893</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.7344398729085891</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>44624.0939927834</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.534238952056007</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>342.1676539209363</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>44624.0939927834</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>488.69675728917116</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$154,A14,'Species'!$U$2:$U$154))</x:f>
-        <x:v>21807650.03124043</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.534238952056007</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>342.1676539209363</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>15268921.549858041</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>6538728.481382389</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.428237741613335</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.4282377416133349</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>2018.5743282607</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.0902393778180124</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>12.309470668609311</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>2018.5743282607</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>12.379753283514807</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$154,A15,'Species'!$U$2:$U$154))</x:f>
-        <x:v>24989.4521683041</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.0902393778180124</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>12.309470668609311</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>24847.58148613283</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>141.87068217126944</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.005709637465137</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.0057096374651370374</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>138335.4183180597</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.846649981462794</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>70.25059088086233</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>138335.4183180597</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>115.59758621479928</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$154,A16,'Species'!$U$2:$U$154))</x:f>
-        <x:v>15991240.44558223</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.846649981462794</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>70.25059088086233</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>9718144.87659496</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>6273095.568987269</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.6455034009726797</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.6455034009726797</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>19893.451649978397</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.2284252913060243</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>169.2097139560889</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>19893.451649978397</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>170.09718292965107</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$154,A17,'Species'!$U$2:$U$154))</x:f>
-        <x:v>3383820.084408544</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.2284252913060243</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>169.2097139560889</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>3366165.263292129</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>17654.821116414852</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.00524478738728</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.005244787387280069</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>37602.6696268138</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.723235579730001</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>528.7319806322635</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>37602.6696268138</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>534.7607259701335</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$154,A18,'Species'!$U$2:$U$154))</x:f>
-        <x:v>20108430.908050038</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.723235579730001</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>528.7319806322635</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>19881733.988845915</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>226696.91920412332</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0114022710157629</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.011402271015762772</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>63461.026477834195</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.364831806442417</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>231.64973431841202</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>63461.026477834195</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>258.3100838382811</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$154,A19,'Species'!$U$2:$U$154))</x:f>
-        <x:v>16392623.069952728</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.364831806442417</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>231.64973431841202</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>14700729.923164</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>1691893.1467887275</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.1150890571850316</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.11508905718503164</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>42532.881166059095</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.4862206772245115</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>306.35196986717943</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>42532.881166059095</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>323.67357253216335</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$154,A20,'Species'!$U$2:$U$154))</x:f>
-        <x:v>13766769.597104313</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.4862206772245115</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>306.35196986717943</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>13030031.92934886</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>736737.6677554529</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0565415090116568</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.056541509011656686</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>8674.151263038999</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.503404236717906</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>318.7162718929465</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>8674.151263038999</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>356.34176484089755</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$154,A21,'Species'!$U$2:$U$154))</x:f>
-        <x:v>3090962.3695682175</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.503404236717906</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>318.7162718929465</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>2764593.152391283</x:v>
       </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>326369.2171769347</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.1180532538375985</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.11805325383759849</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G21">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O21">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7b51d6c3079422e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63ae600f6dbc41bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12920,7 +11716,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -13019,7 +11815,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>545876685.8837115</x:v>
+        <x:v>319692799.8992253</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13033,7 +11829,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>545876685.8837115</x:v>
+        <x:v>384466587.7167525</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13047,7 +11843,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-226183885.98448616</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13061,7 +11857,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-161410098.16695893</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13072,9 +11868,9 @@
         <x:v>EEZ_459</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -13086,47 +11882,19 @@
         <x:v>EEZ_459</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_459</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_459</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b49459241bc4f87"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd78330767ea84598"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13173,7 +11941,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
